--- a/data/processed/merged_aiops.xlsx
+++ b/data/processed/merged_aiops.xlsx
@@ -1334,7 +1334,7 @@
         <v>20</v>
       </c>
       <c r="G29" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="30">
@@ -1466,7 +1466,7 @@
         <v>8</v>
       </c>
       <c r="G33" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="34">
@@ -1664,7 +1664,7 @@
         <v>17</v>
       </c>
       <c r="G39" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="40">
@@ -1829,7 +1829,7 @@
         <v>108</v>
       </c>
       <c r="G44" t="n">
-        <v>50.82</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="45">
@@ -1862,7 +1862,7 @@
         <v>12</v>
       </c>
       <c r="G45" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="46">
@@ -2225,7 +2225,7 @@
         <v>16</v>
       </c>
       <c r="G56" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="57">
@@ -2390,7 +2390,7 @@
         <v>14</v>
       </c>
       <c r="G61" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="62">
@@ -2684,10 +2684,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>249.02</v>
+        <v>274.02</v>
       </c>
       <c r="G70" t="n">
-        <v>241.11</v>
+        <v>241.61</v>
       </c>
     </row>
     <row r="71">
@@ -2935,7 +2935,7 @@
         <v>2.95</v>
       </c>
       <c r="G78" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="79">
@@ -3133,7 +3133,7 @@
         <v>241.17</v>
       </c>
       <c r="G84" t="n">
-        <v>209.87</v>
+        <v>211.09</v>
       </c>
     </row>
     <row r="85">
@@ -3199,7 +3199,7 @@
         <v>2.67</v>
       </c>
       <c r="G86" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="87">
@@ -3265,7 +3265,7 @@
         <v>2.67</v>
       </c>
       <c r="G88" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="89">
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>25.05</v>
+        <v>28.96</v>
       </c>
       <c r="G105" t="n">
-        <v>8.27</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="106">
@@ -4240,7 +4240,7 @@
         <v>1.39</v>
       </c>
       <c r="G119" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="120">
@@ -4372,7 +4372,7 @@
         <v>1.35</v>
       </c>
       <c r="G123" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="124">
@@ -4438,7 +4438,7 @@
         <v>3.96</v>
       </c>
       <c r="G125" t="n">
-        <v>3.69</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="126">
@@ -4801,7 +4801,7 @@
         <v>84.31</v>
       </c>
       <c r="G136" t="n">
-        <v>80.26000000000001</v>
+        <v>80.41</v>
       </c>
     </row>
     <row r="137">
@@ -5560,7 +5560,7 @@
         <v>10.71</v>
       </c>
       <c r="G159" t="n">
-        <v>8.869999999999999</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="160">
@@ -5659,7 +5659,7 @@
         <v>0.98</v>
       </c>
       <c r="G162" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="163">
@@ -5890,7 +5890,7 @@
         <v>18.43</v>
       </c>
       <c r="G169" t="n">
-        <v>11.12</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="170">
@@ -6319,7 +6319,7 @@
         <v>20</v>
       </c>
       <c r="G182" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="183">
@@ -6451,7 +6451,7 @@
         <v>8</v>
       </c>
       <c r="G186" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="187">
@@ -6649,7 +6649,7 @@
         <v>17</v>
       </c>
       <c r="G192" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="193">
@@ -6814,7 +6814,7 @@
         <v>108</v>
       </c>
       <c r="G197" t="n">
-        <v>50.82</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="198">
@@ -6847,7 +6847,7 @@
         <v>12</v>
       </c>
       <c r="G198" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="199">
@@ -7210,7 +7210,7 @@
         <v>16</v>
       </c>
       <c r="G209" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="210">
@@ -7375,7 +7375,7 @@
         <v>14</v>
       </c>
       <c r="G214" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="215">
@@ -7771,7 +7771,7 @@
         <v>6.05</v>
       </c>
       <c r="G226" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="227">
@@ -7936,7 +7936,7 @@
         <v>1.24</v>
       </c>
       <c r="G231" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="232">
@@ -8068,7 +8068,7 @@
         <v>3.22</v>
       </c>
       <c r="G235" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="236">
@@ -8101,7 +8101,7 @@
         <v>3.22</v>
       </c>
       <c r="G236" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="237">
@@ -8167,7 +8167,7 @@
         <v>0.91</v>
       </c>
       <c r="G238" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="239">
@@ -8299,7 +8299,7 @@
         <v>6.34</v>
       </c>
       <c r="G242" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="243">
@@ -8398,7 +8398,7 @@
         <v>12.79</v>
       </c>
       <c r="G245" t="n">
-        <v>6.25</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="246">
@@ -8431,7 +8431,7 @@
         <v>10.54</v>
       </c>
       <c r="G246" t="n">
-        <v>3.92</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="247">
@@ -8794,7 +8794,7 @@
         <v>1.94</v>
       </c>
       <c r="G257" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="258">
@@ -8992,7 +8992,7 @@
         <v>24</v>
       </c>
       <c r="G263" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="264">
@@ -9322,7 +9322,7 @@
         <v>291.95</v>
       </c>
       <c r="G273" t="n">
-        <v>279.55</v>
+        <v>280.02</v>
       </c>
     </row>
     <row r="274">
@@ -9454,7 +9454,7 @@
         <v>293.95</v>
       </c>
       <c r="G277" t="n">
-        <v>285.12</v>
+        <v>285.36</v>
       </c>
     </row>
     <row r="278">
@@ -9616,10 +9616,10 @@
         </is>
       </c>
       <c r="F282" t="n">
-        <v>25.05</v>
+        <v>28.96</v>
       </c>
       <c r="G282" t="n">
-        <v>8.27</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="283">
@@ -9982,7 +9982,7 @@
         <v>8</v>
       </c>
       <c r="G293" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="294">
@@ -10510,7 +10510,7 @@
         <v>1.94</v>
       </c>
       <c r="G309" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="310">
@@ -10576,7 +10576,7 @@
         <v>0.58</v>
       </c>
       <c r="G311" t="n">
-        <v>0.24</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="312">
@@ -10642,7 +10642,7 @@
         <v>141.9</v>
       </c>
       <c r="G313" t="n">
-        <v>135.68</v>
+        <v>136.98</v>
       </c>
     </row>
     <row r="314">
@@ -10675,7 +10675,7 @@
         <v>142</v>
       </c>
       <c r="G314" t="n">
-        <v>137.02</v>
+        <v>137.09</v>
       </c>
     </row>
     <row r="315">
@@ -10774,7 +10774,7 @@
         <v>2.95</v>
       </c>
       <c r="G317" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="318">
@@ -11203,7 +11203,7 @@
         <v>27.91</v>
       </c>
       <c r="G330" t="n">
-        <v>6.4</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="331">
@@ -11236,7 +11236,7 @@
         <v>26.5</v>
       </c>
       <c r="G331" t="n">
-        <v>6.85</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="332">
@@ -11269,7 +11269,7 @@
         <v>76.89</v>
       </c>
       <c r="G332" t="n">
-        <v>49.19</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="333">
@@ -11302,7 +11302,7 @@
         <v>37.94</v>
       </c>
       <c r="G333" t="n">
-        <v>15.23</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="334">
@@ -16357,7 +16357,7 @@
         <v>20</v>
       </c>
       <c r="G508" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="509">
@@ -16477,7 +16477,7 @@
         <v>17</v>
       </c>
       <c r="G512" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="513">
@@ -16626,7 +16626,7 @@
         <v>108</v>
       </c>
       <c r="G517" t="n">
-        <v>50.82</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="518">
@@ -16659,7 +16659,7 @@
         <v>12</v>
       </c>
       <c r="G518" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="519">
@@ -17069,7 +17069,7 @@
         <v>16</v>
       </c>
       <c r="G532" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="533">
@@ -17218,7 +17218,7 @@
         <v>14</v>
       </c>
       <c r="G537" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="538">
@@ -23448,7 +23448,7 @@
         <v>8</v>
       </c>
       <c r="G755" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="756">
@@ -23539,7 +23539,7 @@
         <v>24</v>
       </c>
       <c r="G758" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="759">

--- a/data/processed/merged_aiops.xlsx
+++ b/data/processed/merged_aiops.xlsx
@@ -528,7 +528,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="n">
-        <v>17.41</v>
+        <v>17.46</v>
       </c>
     </row>
     <row r="4">
@@ -561,7 +561,7 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>44.93</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="5">
@@ -627,7 +627,7 @@
         <v>110</v>
       </c>
       <c r="G6" t="n">
-        <v>41.16</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="7">
@@ -660,7 +660,7 @@
         <v>80</v>
       </c>
       <c r="G7" t="n">
-        <v>25.91</v>
+        <v>24.41</v>
       </c>
     </row>
     <row r="8">
@@ -726,7 +726,7 @@
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>29.48</v>
+        <v>29.46</v>
       </c>
     </row>
     <row r="10">
@@ -759,7 +759,7 @@
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>10.85</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="11">
@@ -825,7 +825,7 @@
         <v>220</v>
       </c>
       <c r="G12" t="n">
-        <v>63.57</v>
+        <v>63.86</v>
       </c>
     </row>
     <row r="13">
@@ -858,7 +858,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="14">
@@ -891,7 +891,7 @@
         <v>170</v>
       </c>
       <c r="G14" t="n">
-        <v>47</v>
+        <v>47.04</v>
       </c>
     </row>
     <row r="15">
@@ -1221,7 +1221,7 @@
         <v>15.5</v>
       </c>
       <c r="G24" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="25">
@@ -1419,7 +1419,7 @@
         <v>20</v>
       </c>
       <c r="G30" t="n">
-        <v>2.58</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="31">
@@ -1452,7 +1452,7 @@
         <v>20</v>
       </c>
       <c r="G31" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="32">
@@ -1584,7 +1584,7 @@
         <v>8</v>
       </c>
       <c r="G35" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="36">
@@ -1782,7 +1782,7 @@
         <v>17</v>
       </c>
       <c r="G41" t="n">
-        <v>3.14</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="42">
@@ -1815,7 +1815,7 @@
         <v>17</v>
       </c>
       <c r="G42" t="n">
-        <v>2.51</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="43">
@@ -1980,7 +1980,7 @@
         <v>108</v>
       </c>
       <c r="G47" t="n">
-        <v>36.13</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="48">
@@ -2013,7 +2013,7 @@
         <v>108</v>
       </c>
       <c r="G48" t="n">
-        <v>50.8</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="49">
@@ -2046,7 +2046,7 @@
         <v>12</v>
       </c>
       <c r="G49" t="n">
-        <v>2.79</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="50">
@@ -2079,7 +2079,7 @@
         <v>12</v>
       </c>
       <c r="G50" t="n">
-        <v>2.51</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="51">
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G61" t="n">
-        <v>1.45</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="62">
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G62" t="n">
-        <v>2.13</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="63">
@@ -2640,7 +2640,7 @@
         <v>14</v>
       </c>
       <c r="G67" t="n">
-        <v>4.56</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="68">
@@ -2673,7 +2673,7 @@
         <v>14</v>
       </c>
       <c r="G68" t="n">
-        <v>4.43</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="69">
@@ -3284,7 +3284,7 @@
         <v>45.17</v>
       </c>
       <c r="G87" t="n">
-        <v>13.43</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="88">
@@ -3449,7 +3449,7 @@
         <v>241.17</v>
       </c>
       <c r="G92" t="n">
-        <v>212.28</v>
+        <v>212.31</v>
       </c>
     </row>
     <row r="93">
@@ -4688,7 +4688,7 @@
         <v>1.35</v>
       </c>
       <c r="G131" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="132">
@@ -4721,7 +4721,7 @@
         <v>1.38</v>
       </c>
       <c r="G132" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="133">
@@ -5117,7 +5117,7 @@
         <v>84.31</v>
       </c>
       <c r="G144" t="n">
-        <v>80.59</v>
+        <v>80.66</v>
       </c>
     </row>
     <row r="145">
@@ -5249,7 +5249,7 @@
         <v>0.29</v>
       </c>
       <c r="G148" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="149">
@@ -5876,7 +5876,7 @@
         <v>11.68</v>
       </c>
       <c r="G167" t="n">
-        <v>10.03</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="168">
@@ -6635,7 +6635,7 @@
         <v>20</v>
       </c>
       <c r="G190" t="n">
-        <v>2.58</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="191">
@@ -6668,7 +6668,7 @@
         <v>20</v>
       </c>
       <c r="G191" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="192">
@@ -6800,7 +6800,7 @@
         <v>8</v>
       </c>
       <c r="G195" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="196">
@@ -6998,7 +6998,7 @@
         <v>17</v>
       </c>
       <c r="G201" t="n">
-        <v>3.14</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="202">
@@ -7031,7 +7031,7 @@
         <v>17</v>
       </c>
       <c r="G202" t="n">
-        <v>2.51</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="203">
@@ -7196,7 +7196,7 @@
         <v>108</v>
       </c>
       <c r="G207" t="n">
-        <v>36.13</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="208">
@@ -7229,7 +7229,7 @@
         <v>108</v>
       </c>
       <c r="G208" t="n">
-        <v>50.8</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="209">
@@ -7262,7 +7262,7 @@
         <v>12</v>
       </c>
       <c r="G209" t="n">
-        <v>2.79</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="210">
@@ -7295,7 +7295,7 @@
         <v>12</v>
       </c>
       <c r="G210" t="n">
-        <v>2.51</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="211">
@@ -7655,10 +7655,10 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G221" t="n">
-        <v>1.45</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="222">
@@ -7688,10 +7688,10 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G222" t="n">
-        <v>2.13</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="223">
@@ -7856,7 +7856,7 @@
         <v>14</v>
       </c>
       <c r="G227" t="n">
-        <v>4.56</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="228">
@@ -7889,7 +7889,7 @@
         <v>14</v>
       </c>
       <c r="G228" t="n">
-        <v>4.43</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="229">
@@ -8285,7 +8285,7 @@
         <v>6.05</v>
       </c>
       <c r="G240" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="241">
@@ -8483,7 +8483,7 @@
         <v>12.79</v>
       </c>
       <c r="G246" t="n">
-        <v>10.35</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="247">
@@ -8747,7 +8747,7 @@
         <v>3.81</v>
       </c>
       <c r="G254" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="255">
@@ -8780,7 +8780,7 @@
         <v>1.94</v>
       </c>
       <c r="G255" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="256">
@@ -8912,7 +8912,7 @@
         <v>12.79</v>
       </c>
       <c r="G259" t="n">
-        <v>6.28</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="260">
@@ -8945,7 +8945,7 @@
         <v>10.54</v>
       </c>
       <c r="G260" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="261">
@@ -9539,7 +9539,7 @@
         <v>24</v>
       </c>
       <c r="G278" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="279">
@@ -9605,7 +9605,7 @@
         <v>12</v>
       </c>
       <c r="G280" t="n">
-        <v>6.03</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="281">
@@ -9638,7 +9638,7 @@
         <v>10.49</v>
       </c>
       <c r="G281" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="282">
@@ -9902,7 +9902,7 @@
         <v>291.95</v>
       </c>
       <c r="G289" t="n">
-        <v>280.05</v>
+        <v>280.09</v>
       </c>
     </row>
     <row r="290">
@@ -10595,7 +10595,7 @@
         <v>8</v>
       </c>
       <c r="G310" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="311">
@@ -11285,10 +11285,10 @@
         </is>
       </c>
       <c r="F331" t="n">
-        <v>141.9</v>
+        <v>147.9</v>
       </c>
       <c r="G331" t="n">
-        <v>137.29</v>
+        <v>142.54</v>
       </c>
     </row>
     <row r="332">
@@ -11318,10 +11318,10 @@
         </is>
       </c>
       <c r="F332" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G332" t="n">
-        <v>137.09</v>
+        <v>142.22</v>
       </c>
     </row>
     <row r="333">
@@ -11453,7 +11453,7 @@
         <v>45.17</v>
       </c>
       <c r="G336" t="n">
-        <v>13.43</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="337">
@@ -11849,7 +11849,7 @@
         <v>27.91</v>
       </c>
       <c r="G348" t="n">
-        <v>5.33</v>
+        <v>5.58</v>
       </c>
     </row>
     <row r="349">
@@ -11882,7 +11882,7 @@
         <v>26.5</v>
       </c>
       <c r="G349" t="n">
-        <v>7.03</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="350">
@@ -11912,10 +11912,10 @@
         </is>
       </c>
       <c r="F350" t="n">
-        <v>76.89</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="G350" t="n">
-        <v>60.06</v>
+        <v>63.34</v>
       </c>
     </row>
     <row r="351">
@@ -11945,10 +11945,10 @@
         </is>
       </c>
       <c r="F351" t="n">
-        <v>37.94</v>
+        <v>42.04</v>
       </c>
       <c r="G351" t="n">
-        <v>15.76</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="352">
@@ -15002,7 +15002,7 @@
         <v>15.5</v>
       </c>
       <c r="G457" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="458">
@@ -16455,7 +16455,7 @@
         <v>241.17</v>
       </c>
       <c r="G502" t="n">
-        <v>208.85</v>
+        <v>208.88</v>
       </c>
     </row>
     <row r="503">
@@ -17309,7 +17309,7 @@
         <v>20</v>
       </c>
       <c r="G528" t="n">
-        <v>2.58</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="529">
@@ -17342,7 +17342,7 @@
         <v>20</v>
       </c>
       <c r="G529" t="n">
-        <v>2.65</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="530">
@@ -17474,7 +17474,7 @@
         <v>17</v>
       </c>
       <c r="G533" t="n">
-        <v>3.14</v>
+        <v>2.51</v>
       </c>
     </row>
     <row r="534">
@@ -17507,7 +17507,7 @@
         <v>17</v>
       </c>
       <c r="G534" t="n">
-        <v>2.51</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="535">
@@ -17672,7 +17672,7 @@
         <v>108</v>
       </c>
       <c r="G539" t="n">
-        <v>36.13</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="540">
@@ -17705,7 +17705,7 @@
         <v>108</v>
       </c>
       <c r="G540" t="n">
-        <v>50.8</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="541">
@@ -17738,7 +17738,7 @@
         <v>12</v>
       </c>
       <c r="G541" t="n">
-        <v>2.79</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="542">
@@ -17771,7 +17771,7 @@
         <v>12</v>
       </c>
       <c r="G542" t="n">
-        <v>2.51</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="543">
@@ -18230,10 +18230,10 @@
         </is>
       </c>
       <c r="F556" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G556" t="n">
-        <v>1.45</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="557">
@@ -18263,10 +18263,10 @@
         </is>
       </c>
       <c r="F557" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G557" t="n">
-        <v>2.13</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="558">
@@ -18431,7 +18431,7 @@
         <v>14</v>
       </c>
       <c r="G562" t="n">
-        <v>4.56</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="563">
@@ -18464,7 +18464,7 @@
         <v>14</v>
       </c>
       <c r="G563" t="n">
-        <v>4.43</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="564">
@@ -18629,7 +18629,7 @@
         <v>6.05</v>
       </c>
       <c r="G568" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
     </row>
     <row r="569">
@@ -18827,7 +18827,7 @@
         <v>12.79</v>
       </c>
       <c r="G574" t="n">
-        <v>10.9</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="575">
@@ -19256,7 +19256,7 @@
         <v>12.79</v>
       </c>
       <c r="G587" t="n">
-        <v>8.529999999999999</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="588">
@@ -19289,7 +19289,7 @@
         <v>10.54</v>
       </c>
       <c r="G588" t="n">
-        <v>4.58</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="589">
@@ -19553,7 +19553,7 @@
         <v>1.01</v>
       </c>
       <c r="G596" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="597">
@@ -19619,7 +19619,7 @@
         <v>1.01</v>
       </c>
       <c r="G598" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="599">
@@ -19817,7 +19817,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="G604" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="605">
@@ -19850,7 +19850,7 @@
         <v>0.91</v>
       </c>
       <c r="G605" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="606">
@@ -20015,7 +20015,7 @@
         <v>17.87</v>
       </c>
       <c r="G610" t="n">
-        <v>6.64</v>
+        <v>6.65</v>
       </c>
     </row>
     <row r="611">
@@ -20180,7 +20180,7 @@
         <v>1</v>
       </c>
       <c r="G615" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="616">
@@ -20246,7 +20246,7 @@
         <v>1.03</v>
       </c>
       <c r="G617" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="618">
@@ -20906,7 +20906,7 @@
         <v>2.27</v>
       </c>
       <c r="G637" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="638">
@@ -22163,7 +22163,7 @@
         <v>1.12</v>
       </c>
       <c r="G678" t="n">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="679">
@@ -22229,7 +22229,7 @@
         <v>0.6</v>
       </c>
       <c r="G680" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="681">
@@ -22988,7 +22988,7 @@
         <v>84.31</v>
       </c>
       <c r="G703" t="n">
-        <v>79.64</v>
+        <v>79.70999999999999</v>
       </c>
     </row>
     <row r="704">
@@ -23054,7 +23054,7 @@
         <v>45.39</v>
       </c>
       <c r="G705" t="n">
-        <v>37.94</v>
+        <v>37.96</v>
       </c>
     </row>
     <row r="706">
@@ -23945,7 +23945,7 @@
         <v>9.15</v>
       </c>
       <c r="G732" t="n">
-        <v>7.99</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="733">
@@ -24341,7 +24341,7 @@
         <v>11.45</v>
       </c>
       <c r="G744" t="n">
-        <v>10.12</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="745">
@@ -24770,7 +24770,7 @@
         <v>18.18</v>
       </c>
       <c r="G757" t="n">
-        <v>13.37</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="758">
@@ -24803,7 +24803,7 @@
         <v>34.93</v>
       </c>
       <c r="G758" t="n">
-        <v>12.95</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="759">
@@ -24836,7 +24836,7 @@
         <v>34.74</v>
       </c>
       <c r="G759" t="n">
-        <v>28.2</v>
+        <v>28.29</v>
       </c>
     </row>
     <row r="760">
@@ -24869,7 +24869,7 @@
         <v>25.49</v>
       </c>
       <c r="G760" t="n">
-        <v>21.02</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="761">
@@ -24965,7 +24965,7 @@
         </is>
       </c>
       <c r="F763" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="G763" t="n">
         <v>0.78</v>
@@ -24998,7 +24998,7 @@
         </is>
       </c>
       <c r="F764" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="G764" t="n">
         <v>0.16</v>
@@ -25031,7 +25031,7 @@
         </is>
       </c>
       <c r="F765" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="G765" t="n">
         <v>0.07000000000000001</v>
@@ -25331,7 +25331,7 @@
         <v>293.95</v>
       </c>
       <c r="G774" t="n">
-        <v>284.15</v>
+        <v>284.19</v>
       </c>
     </row>
     <row r="775">
@@ -26090,7 +26090,7 @@
         <v>8</v>
       </c>
       <c r="G797" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="798">
@@ -26222,7 +26222,7 @@
         <v>24</v>
       </c>
       <c r="G801" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
     </row>
     <row r="802">
@@ -26486,7 +26486,7 @@
         <v>12</v>
       </c>
       <c r="G809" t="n">
-        <v>6.03</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="810">
@@ -26519,7 +26519,7 @@
         <v>10.49</v>
       </c>
       <c r="G810" t="n">
-        <v>6.53</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="811">
@@ -27011,10 +27011,10 @@
         </is>
       </c>
       <c r="F825" t="n">
-        <v>141.9</v>
+        <v>147.9</v>
       </c>
       <c r="G825" t="n">
-        <v>136</v>
+        <v>140.9</v>
       </c>
     </row>
     <row r="826">
@@ -27044,10 +27044,10 @@
         </is>
       </c>
       <c r="F826" t="n">
-        <v>141.9</v>
+        <v>147.9</v>
       </c>
       <c r="G826" t="n">
-        <v>135.61</v>
+        <v>141.13</v>
       </c>
     </row>
     <row r="827">
@@ -27077,10 +27077,10 @@
         </is>
       </c>
       <c r="F827" t="n">
-        <v>142.86</v>
+        <v>148.86</v>
       </c>
       <c r="G827" t="n">
-        <v>139.64</v>
+        <v>144.76</v>
       </c>
     </row>
     <row r="828">
@@ -27212,7 +27212,7 @@
         <v>2.29</v>
       </c>
       <c r="G831" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="832">
@@ -27707,7 +27707,7 @@
         <v>241.17</v>
       </c>
       <c r="G846" t="n">
-        <v>208.85</v>
+        <v>208.88</v>
       </c>
     </row>
     <row r="847">
@@ -27971,7 +27971,7 @@
         <v>27.91</v>
       </c>
       <c r="G854" t="n">
-        <v>22.76</v>
+        <v>23.39</v>
       </c>
     </row>
     <row r="855">
@@ -28004,7 +28004,7 @@
         <v>26.5</v>
       </c>
       <c r="G855" t="n">
-        <v>7.08</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="856">
@@ -28034,10 +28034,10 @@
         </is>
       </c>
       <c r="F856" t="n">
-        <v>76.89</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="G856" t="n">
-        <v>60.57</v>
+        <v>64.81999999999999</v>
       </c>
     </row>
     <row r="857">
@@ -28067,10 +28067,10 @@
         </is>
       </c>
       <c r="F857" t="n">
-        <v>37.94</v>
+        <v>42.04</v>
       </c>
       <c r="G857" t="n">
-        <v>16.55</v>
+        <v>19.58</v>
       </c>
     </row>
     <row r="858">
@@ -30887,7 +30887,7 @@
         <v>100</v>
       </c>
       <c r="G954" t="n">
-        <v>41.53</v>
+        <v>41.79</v>
       </c>
     </row>
     <row r="955">
@@ -30953,7 +30953,7 @@
         <v>120</v>
       </c>
       <c r="G956" t="n">
-        <v>36.03</v>
+        <v>36.09</v>
       </c>
     </row>
     <row r="957">
@@ -31052,7 +31052,7 @@
         <v>80</v>
       </c>
       <c r="G959" t="n">
-        <v>18.57</v>
+        <v>18.58</v>
       </c>
     </row>
     <row r="960">
@@ -31085,7 +31085,7 @@
         <v>100</v>
       </c>
       <c r="G960" t="n">
-        <v>34.26</v>
+        <v>34.29</v>
       </c>
     </row>
     <row r="961">
@@ -31151,7 +31151,7 @@
         <v>90</v>
       </c>
       <c r="G962" t="n">
-        <v>27.82</v>
+        <v>27.84</v>
       </c>
     </row>
   </sheetData>
